--- a/library/digital.xlsx
+++ b/library/digital.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067AC93A-E232-454A-B49A-597E7B37E91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797CAD1E-C483-41F8-8D87-011079CD42C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11925" yWindow="4890" windowWidth="13530" windowHeight="10395" firstSheet="1" activeTab="5" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="clock" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="158">
   <si>
     <t>Part Number</t>
   </si>
@@ -504,6 +504,15 @@
   </si>
   <si>
     <t>20-TSSOP</t>
+  </si>
+  <si>
+    <t>MS51FB9AE</t>
+  </si>
+  <si>
+    <t>MS51FB9AE 20-TSSOP</t>
+  </si>
+  <si>
+    <t>Nuvoton</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4D8C3D-D832-496B-AB92-259D2AD291EC}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1391,6 +1400,29 @@
         <v>83</v>
       </c>
       <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>157</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/library/digital.xlsx
+++ b/library/digital.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797CAD1E-C483-41F8-8D87-011079CD42C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED35FEF6-85C2-4790-B96E-42BEAE3A1E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="163">
   <si>
     <t>Part Number</t>
   </si>
@@ -513,6 +513,21 @@
   </si>
   <si>
     <t>Nuvoton</t>
+  </si>
+  <si>
+    <t>AT32F421</t>
+  </si>
+  <si>
+    <t>AT32F421K8U7</t>
+  </si>
+  <si>
+    <t>32-QFN (4x4)</t>
+  </si>
+  <si>
+    <t>AT32F421K8U7 32-QFN (4x4)</t>
+  </si>
+  <si>
+    <t>Artery</t>
   </si>
 </sst>
 </file>
@@ -1104,11 +1119,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4D8C3D-D832-496B-AB92-259D2AD291EC}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
     <col min="3" max="3" width="26.85546875" customWidth="1"/>
     <col min="4" max="4" width="26.5703125" customWidth="1"/>
     <col min="5" max="5" width="19.140625" customWidth="1"/>
@@ -1422,6 +1437,29 @@
       </c>
       <c r="G13" s="2" t="s">
         <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>159</v>
+      </c>
+      <c r="B14" t="s">
+        <v>160</v>
+      </c>
+      <c r="C14" t="s">
+        <v>161</v>
+      </c>
+      <c r="D14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14" t="s">
+        <v>158</v>
+      </c>
+      <c r="F14" t="s">
+        <v>160</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/library/digital.xlsx
+++ b/library/digital.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED35FEF6-85C2-4790-B96E-42BEAE3A1E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBD7792-448D-4597-923B-D6587091974A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="166">
   <si>
     <t>Part Number</t>
   </si>
@@ -528,6 +528,15 @@
   </si>
   <si>
     <t>Artery</t>
+  </si>
+  <si>
+    <t>STM8S003F3P6TR</t>
+  </si>
+  <si>
+    <t>STM8S003F3P6TR 20-TSSOP</t>
+  </si>
+  <si>
+    <t>STM8S003</t>
   </si>
 </sst>
 </file>
@@ -1119,7 +1128,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4D8C3D-D832-496B-AB92-259D2AD291EC}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1128,6 +1137,8 @@
     <col min="4" max="4" width="26.5703125" customWidth="1"/>
     <col min="5" max="5" width="19.140625" customWidth="1"/>
     <col min="6" max="6" width="21.85546875" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1460,6 +1471,29 @@
       </c>
       <c r="G14" s="2" t="s">
         <v>162</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>163</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C15" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" t="s">
+        <v>163</v>
+      </c>
+      <c r="E15" t="s">
+        <v>165</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/library/digital.xlsx
+++ b/library/digital.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\elem_altium_db2\library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBD7792-448D-4597-923B-D6587091974A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08280C7D-EC89-421F-A5CD-AB3DFB6C8C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="clock" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="169">
   <si>
     <t>Part Number</t>
   </si>
@@ -537,6 +537,15 @@
   </si>
   <si>
     <t>STM8S003</t>
+  </si>
+  <si>
+    <t>M25PE16</t>
+  </si>
+  <si>
+    <t>M25PE16 8-SOIC</t>
+  </si>
+  <si>
+    <t>Micron</t>
   </si>
 </sst>
 </file>
@@ -1646,7 +1655,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -1655,6 +1664,7 @@
     <col min="4" max="4" width="21.85546875" customWidth="1"/>
     <col min="5" max="5" width="23.140625" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1957,6 +1967,29 @@
       </c>
       <c r="G13" s="2" t="s">
         <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>166</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D14" t="s">
+        <v>166</v>
+      </c>
+      <c r="E14" t="s">
+        <v>166</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/library/digital.xlsx
+++ b/library/digital.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08280C7D-EC89-421F-A5CD-AB3DFB6C8C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F6BF2A-857A-4B3C-89BF-ED2E3424C95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="clock" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="176">
   <si>
     <t>Part Number</t>
   </si>
@@ -546,13 +546,65 @@
   </si>
   <si>
     <t>Micron</t>
+  </si>
+  <si>
+    <t>74HC273D</t>
+  </si>
+  <si>
+    <t>20-SOIC</t>
+  </si>
+  <si>
+    <t>74HC273D 20-SOIC</t>
+  </si>
+  <si>
+    <t>74HC273D,653</t>
+  </si>
+  <si>
+    <r>
+      <t>ULN2803A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t>DW</t>
+    </r>
+  </si>
+  <si>
+    <t>18-SOIC</t>
+  </si>
+  <si>
+    <r>
+      <t>ULN2803A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t>DW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 18-SOIC</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -567,6 +619,11 @@
       <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Inter"/>
     </font>
   </fonts>
   <fills count="3">
@@ -596,10 +653,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
@@ -916,7 +974,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" customWidth="1"/>
@@ -926,7 +984,7 @@
     <col min="6" max="6" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -952,7 +1010,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
@@ -975,7 +1033,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
         <v>28</v>
       </c>
@@ -995,7 +1053,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
         <v>30</v>
       </c>
@@ -1025,17 +1083,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="10.28515625" customWidth="1"/>
+    <col min="7" max="7" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1061,7 +1120,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -1084,7 +1143,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1107,7 +1166,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
         <v>36</v>
       </c>
@@ -1127,6 +1186,29 @@
         <v>18</v>
       </c>
       <c r="G4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F5" t="s">
+        <v>170</v>
+      </c>
+      <c r="G5" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1138,7 +1220,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4D8C3D-D832-496B-AB92-259D2AD291EC}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
@@ -1150,7 +1232,7 @@
     <col min="8" max="8" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1176,7 +1258,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
         <v>40</v>
       </c>
@@ -1200,7 +1282,7 @@
       </c>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
         <v>44</v>
       </c>
@@ -1224,7 +1306,7 @@
       </c>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
         <v>49</v>
       </c>
@@ -1248,7 +1330,7 @@
       </c>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
         <v>54</v>
       </c>
@@ -1270,7 +1352,7 @@
       </c>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
         <v>57</v>
       </c>
@@ -1292,7 +1374,7 @@
       </c>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
         <v>59</v>
       </c>
@@ -1316,7 +1398,7 @@
       </c>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
         <v>65</v>
       </c>
@@ -1340,7 +1422,7 @@
       </c>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
         <v>68</v>
       </c>
@@ -1364,7 +1446,7 @@
       </c>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
         <v>70</v>
       </c>
@@ -1388,7 +1470,7 @@
       </c>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
         <v>73</v>
       </c>
@@ -1412,7 +1494,7 @@
       </c>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
         <v>79</v>
       </c>
@@ -1436,7 +1518,7 @@
       </c>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
         <v>155</v>
       </c>
@@ -1459,7 +1541,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>159</v>
       </c>
@@ -1482,7 +1564,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>163</v>
       </c>
@@ -1513,7 +1595,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD41208-6905-41A5-8CDA-45891F714057}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
@@ -1522,7 +1604,7 @@
     <col min="5" max="5" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1548,7 +1630,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
         <v>84</v>
       </c>
@@ -1568,7 +1650,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -1588,7 +1670,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -1608,7 +1690,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>96</v>
       </c>
@@ -1628,7 +1710,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="12.75" customHeight="1">
       <c r="A6" t="s">
         <v>100</v>
       </c>
@@ -1656,7 +1738,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
@@ -1667,7 +1749,7 @@
     <col min="7" max="7" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1693,7 +1775,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>102</v>
       </c>
@@ -1716,7 +1798,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
         <v>106</v>
       </c>
@@ -1739,7 +1821,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
         <v>110</v>
       </c>
@@ -1762,7 +1844,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
         <v>112</v>
       </c>
@@ -1785,7 +1867,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
         <v>118</v>
       </c>
@@ -1808,7 +1890,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
         <v>122</v>
       </c>
@@ -1831,7 +1913,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
         <v>124</v>
       </c>
@@ -1854,7 +1936,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
         <v>126</v>
       </c>
@@ -1877,7 +1959,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
         <v>128</v>
       </c>
@@ -1900,7 +1982,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>131</v>
       </c>
@@ -1923,7 +2005,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
         <v>134</v>
       </c>
@@ -1946,7 +2028,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
         <v>137</v>
       </c>
@@ -1969,7 +2051,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>166</v>
       </c>
@@ -1999,17 +2081,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B396063C-A3E8-4F0D-BBD3-83031D2833E6}">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" customWidth="1"/>
     <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2035,7 +2118,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
         <v>140</v>
       </c>
@@ -2058,7 +2141,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>143</v>
       </c>
@@ -2081,7 +2164,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>146</v>
       </c>
@@ -2104,7 +2187,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>150</v>
       </c>
@@ -2124,6 +2207,26 @@
         <v>154</v>
       </c>
       <c r="G5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F6" t="s">
+        <v>174</v>
+      </c>
+      <c r="G6" t="s">
         <v>10</v>
       </c>
     </row>

--- a/library/digital.xlsx
+++ b/library/digital.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F6BF2A-857A-4B3C-89BF-ED2E3424C95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27099C2-5865-400C-807A-95C33BBBE34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="176">
   <si>
     <t>Part Number</t>
   </si>
@@ -653,11 +653,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
@@ -2088,6 +2087,7 @@
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" customWidth="1"/>
+    <col min="5" max="5" width="21.140625" customWidth="1"/>
     <col min="6" max="6" width="14.140625" customWidth="1"/>
     <col min="7" max="7" width="25.28515625" customWidth="1"/>
   </cols>
@@ -2211,16 +2211,19 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="3" t="s">
+      <c r="A6" t="s">
         <v>173</v>
       </c>
       <c r="B6" t="s">
         <v>174</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" t="s">
         <v>175</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E6" t="s">
         <v>173</v>
       </c>
       <c r="F6" t="s">

--- a/library/digital.xlsx
+++ b/library/digital.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27099C2-5865-400C-807A-95C33BBBE34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC9BA38-ACEF-4A81-9543-72F1647A79F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="177">
   <si>
     <t>Part Number</t>
   </si>
@@ -598,6 +598,9 @@
       </rPr>
       <t xml:space="preserve"> 18-SOIC</t>
     </r>
+  </si>
+  <si>
+    <t>ULN2803A</t>
   </si>
 </sst>
 </file>
@@ -2224,7 +2227,7 @@
         <v>173</v>
       </c>
       <c r="E6" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F6" t="s">
         <v>174</v>

--- a/library/digital.xlsx
+++ b/library/digital.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC9BA38-ACEF-4A81-9543-72F1647A79F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89CAC84-0339-4C14-B560-4EFBC483C40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="2670" yWindow="1920" windowWidth="23085" windowHeight="13635" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="clock" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="181">
   <si>
     <t>Part Number</t>
   </si>
@@ -601,6 +601,18 @@
   </si>
   <si>
     <t>ULN2803A</t>
+  </si>
+  <si>
+    <t>SN74LVC1G08</t>
+  </si>
+  <si>
+    <t>SN74LVC1G08DRL</t>
+  </si>
+  <si>
+    <t>DRL</t>
+  </si>
+  <si>
+    <t>SN74LVC1G08DRL DRL</t>
   </si>
 </sst>
 </file>
@@ -1085,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -1214,8 +1226,32 @@
         <v>39</v>
       </c>
     </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F6" t="s">
+        <v>179</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/library/digital.xlsx
+++ b/library/digital.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garou/Documents/work/elem_altium_db2/library/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89CAC84-0339-4C14-B560-4EFBC483C40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54B267F-827B-EF4A-B40E-8693AF502F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2670" yWindow="1920" windowWidth="23085" windowHeight="13635" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="clock" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="189">
   <si>
     <t>Part Number</t>
   </si>
@@ -107,9 +107,6 @@
     <t>14-TSSOP</t>
   </si>
   <si>
-    <t>74ACT74MTC TSSOP-16</t>
-  </si>
-  <si>
     <t>74ACT04MTC</t>
   </si>
   <si>
@@ -167,21 +164,12 @@
     <t>32-LQFP</t>
   </si>
   <si>
-    <t>ATmega8A-AU 32-LQFP</t>
-  </si>
-  <si>
     <t>Microchip Technology</t>
   </si>
   <si>
     <t>CC2640R2FRGZT</t>
   </si>
   <si>
-    <t>48-VFQFN</t>
-  </si>
-  <si>
-    <t>CC2640R2FRGZT 48-VFQFN</t>
-  </si>
-  <si>
     <t>CC2640RGZ</t>
   </si>
   <si>
@@ -191,12 +179,6 @@
     <t>CC2640R2FRHBT</t>
   </si>
   <si>
-    <t>32-VFQFN</t>
-  </si>
-  <si>
-    <t>CC2640R2FRHBT 32-VFQFN</t>
-  </si>
-  <si>
     <t>CC2640RHB</t>
   </si>
   <si>
@@ -284,9 +266,6 @@
     <t>176-LQFP</t>
   </si>
   <si>
-    <t>STM32H743IIT6 176-LQFP</t>
-  </si>
-  <si>
     <t>STM32H74xxI/G</t>
   </si>
   <si>
@@ -299,9 +278,6 @@
     <t>LQFP-144</t>
   </si>
   <si>
-    <t>К1986ВЕ1QI LQFP144</t>
-  </si>
-  <si>
     <t>1986ВЕ1Q</t>
   </si>
   <si>
@@ -323,9 +299,6 @@
     <t>LQFP-64</t>
   </si>
   <si>
-    <t>К1986ВЕ92QI LQFP64</t>
-  </si>
-  <si>
     <t>1986ВЕ92Q</t>
   </si>
   <si>
@@ -383,9 +356,6 @@
     <t>8-LGA</t>
   </si>
   <si>
-    <t>AS5F18G04SND-10LIN 8-LGA</t>
-  </si>
-  <si>
     <t>AS5F18G04SND-10LIN</t>
   </si>
   <si>
@@ -437,18 +407,9 @@
     <t>GD25Q16ETIGR</t>
   </si>
   <si>
-    <t>SOP8</t>
-  </si>
-  <si>
-    <t>GD25Q16ETIGR SOP8</t>
-  </si>
-  <si>
     <t>ZD25Q64BSIGT</t>
   </si>
   <si>
-    <t>ZD25Q64BSIGT SOP8</t>
-  </si>
-  <si>
     <t>Zetta</t>
   </si>
   <si>
@@ -458,9 +419,6 @@
     <t>54-TSOP</t>
   </si>
   <si>
-    <t>W9812G6KH-6 54-TSOP</t>
-  </si>
-  <si>
     <t>ICS-43434</t>
   </si>
   <si>
@@ -485,9 +443,6 @@
     <t>4-LSOP</t>
   </si>
   <si>
-    <t>EL1019 4-LSOP</t>
-  </si>
-  <si>
     <t>UMW</t>
   </si>
   <si>
@@ -509,9 +464,6 @@
     <t>MS51FB9AE</t>
   </si>
   <si>
-    <t>MS51FB9AE 20-TSSOP</t>
-  </si>
-  <si>
     <t>Nuvoton</t>
   </si>
   <si>
@@ -524,27 +476,18 @@
     <t>32-QFN (4x4)</t>
   </si>
   <si>
-    <t>AT32F421K8U7 32-QFN (4x4)</t>
-  </si>
-  <si>
     <t>Artery</t>
   </si>
   <si>
     <t>STM8S003F3P6TR</t>
   </si>
   <si>
-    <t>STM8S003F3P6TR 20-TSSOP</t>
-  </si>
-  <si>
     <t>STM8S003</t>
   </si>
   <si>
     <t>M25PE16</t>
   </si>
   <si>
-    <t>M25PE16 8-SOIC</t>
-  </si>
-  <si>
     <t>Micron</t>
   </si>
   <si>
@@ -552,9 +495,6 @@
   </si>
   <si>
     <t>20-SOIC</t>
-  </si>
-  <si>
-    <t>74HC273D 20-SOIC</t>
   </si>
   <si>
     <t>74HC273D,653</t>
@@ -574,6 +514,102 @@
   </si>
   <si>
     <t>18-SOIC</t>
+  </si>
+  <si>
+    <t>ULN2803A</t>
+  </si>
+  <si>
+    <t>SN74LVC1G08</t>
+  </si>
+  <si>
+    <t>SN74LVC1G08DRL</t>
+  </si>
+  <si>
+    <t>DRL</t>
+  </si>
+  <si>
+    <t>SN74LVC1G08DRL DRL</t>
+  </si>
+  <si>
+    <t>74ACT74MTC TSSOP-14</t>
+  </si>
+  <si>
+    <t>SOIC-20</t>
+  </si>
+  <si>
+    <t>74HC273D SOIC-20</t>
+  </si>
+  <si>
+    <t>LQFP-32</t>
+  </si>
+  <si>
+    <t>ATmega8A-AU LQFP-32</t>
+  </si>
+  <si>
+    <t>VFQFN-48</t>
+  </si>
+  <si>
+    <t>CC2640R2FRGZT VFQFN-48</t>
+  </si>
+  <si>
+    <t>CC2640R2FRHBT VFQFN-32</t>
+  </si>
+  <si>
+    <t>VFQFN-32</t>
+  </si>
+  <si>
+    <t>LQFP-176</t>
+  </si>
+  <si>
+    <t>STM32H743IIT6 LQFP-176</t>
+  </si>
+  <si>
+    <t>MS51FB9AE TSSOP-20</t>
+  </si>
+  <si>
+    <t>AT32F421K8U7 QFN-32 (4x4)</t>
+  </si>
+  <si>
+    <t>QFN-32 (4x4)</t>
+  </si>
+  <si>
+    <t>STM8S003F3P6TR TSSOP-20</t>
+  </si>
+  <si>
+    <t>К1986ВЕ1QI LQFP-144</t>
+  </si>
+  <si>
+    <t>К1986ВЕ92QI LQFP-64</t>
+  </si>
+  <si>
+    <t>LGA-8</t>
+  </si>
+  <si>
+    <t>AS5F18G04SND-10LIN LGA-8</t>
+  </si>
+  <si>
+    <t>GD25Q16ETIGR SOP-8</t>
+  </si>
+  <si>
+    <t>ZD25Q64BSIGT SOP-8</t>
+  </si>
+  <si>
+    <t>SOP-8</t>
+  </si>
+  <si>
+    <t>TSOP-54</t>
+  </si>
+  <si>
+    <t>W9812G6KH-6 TSOP-54</t>
+  </si>
+  <si>
+    <t>M25PE16 SOIC-8</t>
+  </si>
+  <si>
+    <t>LSOP-4</t>
+  </si>
+  <si>
+    <t>EL1019 LSOP-4</t>
   </si>
   <si>
     <r>
@@ -596,23 +632,11 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 18-SOIC</t>
+      <t xml:space="preserve"> SOIC-18</t>
     </r>
   </si>
   <si>
-    <t>ULN2803A</t>
-  </si>
-  <si>
-    <t>SN74LVC1G08</t>
-  </si>
-  <si>
-    <t>SN74LVC1G08DRL</t>
-  </si>
-  <si>
-    <t>DRL</t>
-  </si>
-  <si>
-    <t>SN74LVC1G08DRL DRL</t>
+    <t>SOIC-18</t>
   </si>
 </sst>
 </file>
@@ -674,8 +698,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -691,9 +715,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -731,7 +755,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -837,7 +861,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -979,7 +1003,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -988,14 +1012,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1026,68 +1047,68 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
         <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>31</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
         <v>32</v>
       </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>33</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>34</v>
-      </c>
-      <c r="G4" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1098,14 +1119,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1139,10 +1157,10 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="D2" t="s">
         <v>20</v>
@@ -1159,19 +1177,19 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
@@ -1182,68 +1200,68 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
         <v>37</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" t="s">
-        <v>38</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="B5" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D5" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="E5" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F5" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="B6" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="C6" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="E6" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="F6" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="G6" t="s">
         <v>10</v>
@@ -1258,16 +1276,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4D8C3D-D832-496B-AB92-259D2AD291EC}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1298,46 +1311,46 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>10</v>
@@ -1346,22 +1359,22 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>50</v>
+        <v>168</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>51</v>
+        <v>167</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>10</v>
@@ -1370,138 +1383,138 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>10</v>
@@ -1510,119 +1523,119 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="B14" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C14" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="D14" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="E14" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="F14" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="C15" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="D15" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="E15" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1633,13 +1646,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD41208-6905-41A5-8CDA-45891F714057}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1670,59 +1681,59 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>175</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>176</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>13</v>
@@ -1730,39 +1741,39 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="12.75" customHeight="1">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>14</v>
@@ -1776,15 +1787,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="25.85546875" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1815,22 +1822,22 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G2" t="s">
         <v>19</v>
@@ -1838,278 +1845,278 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="F3" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="H3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>114</v>
+        <v>178</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
       </c>
       <c r="G8" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B11" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="C11" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G12" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="B13" t="s">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="F13" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="D14" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="E14" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2120,15 +2127,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B396063C-A3E8-4F0D-BBD3-83031D2833E6}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" customWidth="1"/>
-    <col min="5" max="5" width="21.140625" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="25.28515625" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2159,42 +2162,42 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="F2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="G2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -2205,45 +2208,45 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="D4" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="E4" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F4" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="G4" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C5" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
@@ -2251,22 +2254,22 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C6" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D6" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="E6" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="F6" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="G6" t="s">
         <v>10</v>

--- a/library/digital.xlsx
+++ b/library/digital.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garou/Documents/work/elem_altium_db2/library/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54B267F-827B-EF4A-B40E-8693AF502F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D41D920-F00D-45FC-8E07-F498F655B69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="clock" sheetId="1" r:id="rId1"/>
@@ -34,12 +34,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="192">
   <si>
     <t>Part Number</t>
   </si>
@@ -638,12 +641,58 @@
   <si>
     <t>SOIC-18</t>
   </si>
+  <si>
+    <t>SN74AHCT1G86</t>
+  </si>
+  <si>
+    <r>
+      <t>SN74AHCT1G86</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DBV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SN74AHCT1G86</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DBV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> SOT23-5</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -663,6 +712,14 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Inter"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -698,8 +755,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1012,11 +1069,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1118,12 +1175,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1264,6 +1321,29 @@
         <v>158</v>
       </c>
       <c r="G6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1276,11 +1356,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4D8C3D-D832-496B-AB92-259D2AD291EC}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1646,11 +1726,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD41208-6905-41A5-8CDA-45891F714057}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1787,11 +1867,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2127,11 +2207,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B396063C-A3E8-4F0D-BBD3-83031D2833E6}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">

--- a/library/digital.xlsx
+++ b/library/digital.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\elem_altium_db2\library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D41D920-F00D-45FC-8E07-F498F655B69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC32484-DC91-4263-B494-D1426926FE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="clock" sheetId="1" r:id="rId1"/>
@@ -34,15 +34,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="195">
   <si>
     <t>Part Number</t>
   </si>
@@ -686,6 +683,15 @@
       </rPr>
       <t xml:space="preserve"> SOT23-5</t>
     </r>
+  </si>
+  <si>
+    <t>NE555</t>
+  </si>
+  <si>
+    <t>NE555D</t>
+  </si>
+  <si>
+    <t>NE555 8-SOIC</t>
   </si>
 </sst>
 </file>
@@ -772,9 +778,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -812,7 +818,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -918,7 +924,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1060,7 +1066,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1068,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.85546875" customWidth="1"/>
@@ -1149,24 +1155,137 @@
       <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>34</v>
       </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/library/digital.xlsx
+++ b/library/digital.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC32484-DC91-4263-B494-D1426926FE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B29057-303D-4805-A0A9-3BD97797B71A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="clock" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="198">
   <si>
     <t>Part Number</t>
   </si>
@@ -692,6 +692,15 @@
   </si>
   <si>
     <t>NE555 8-SOIC</t>
+  </si>
+  <si>
+    <t>SN74LVC1G02DBVR</t>
+  </si>
+  <si>
+    <t>SN74LVC1G02DBV</t>
+  </si>
+  <si>
+    <t>SN74LVC1G02DBV SOT23-5</t>
   </si>
 </sst>
 </file>
@@ -1294,7 +1303,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.85546875" customWidth="1"/>
@@ -1375,16 +1384,16 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>35</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>35</v>
       </c>
       <c r="E4" t="s">
@@ -1463,6 +1472,29 @@
         <v>18</v>
       </c>
       <c r="G7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D8" t="s">
+        <v>196</v>
+      </c>
+      <c r="E8" t="s">
+        <v>195</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
         <v>10</v>
       </c>
     </row>

--- a/library/digital.xlsx
+++ b/library/digital.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B29057-303D-4805-A0A9-3BD97797B71A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9099BC82-C472-4DB6-80E0-8D8C74DD44C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="clock" sheetId="1" r:id="rId1"/>
@@ -34,12 +34,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="200">
   <si>
     <t>Part Number</t>
   </si>
@@ -701,6 +704,12 @@
   </si>
   <si>
     <t>SN74LVC1G02DBV SOT23-5</t>
+  </si>
+  <si>
+    <t>ISO1540</t>
+  </si>
+  <si>
+    <t>ISO1540DR</t>
   </si>
 </sst>
 </file>
@@ -787,9 +796,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -827,7 +836,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -933,7 +942,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1075,7 +1084,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2357,7 +2366,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B396063C-A3E8-4F0D-BBD3-83031D2833E6}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.85546875" customWidth="1"/>
@@ -2506,6 +2515,27 @@
         <v>10</v>
       </c>
     </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>199</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="str">
+        <f>_xlfn.CONCAT(D7, " ", B7)</f>
+        <v>ISO1540DR 8-SOIC</v>
+      </c>
+      <c r="D7" t="s">
+        <v>199</v>
+      </c>
+      <c r="E7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
